--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C2" s="28" t="inlineStr">
         <is>
-          <t>Ruote di reazione</t>
+          <t>Ruote di reazione (4 in piramide, classe 0,1 N·m·s)</t>
         </is>
       </c>
       <c r="D2" s="30" t="inlineStr">
@@ -1164,12 +1164,18 @@
       <c r="E2" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="n"/>
+      <c r="F2" s="31" t="n">
+        <v>0.33</v>
+      </c>
       <c r="G2" s="32">
         <f>IF(OR(E2="",F2=""),"",E2*F2)</f>
         <v/>
       </c>
-      <c r="H2" s="30" t="n"/>
+      <c r="H2" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I2" s="33">
         <f>IF(H2="","",INDEX(Liste!$B$2:$B$4,MATCH(H2,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1180,11 +1186,19 @@
       </c>
       <c r="K2" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L2" s="30" t="inlineStr">
+        <is>
+          <t>D-048</t>
+        </is>
+      </c>
+      <c r="M2" s="30" t="inlineStr">
+        <is>
+          <t>BCT RWp100 (dati indicativi del costruttore). Alternativa W4: 4 × RW-0.06 da 0,233 kg</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="22">
       <c r="A3" s="28" t="inlineStr">
@@ -1289,7 +1303,7 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>Magnetorquer</t>
+          <t>Magnetorquer (3 barre, ≥ 2,5 A·m²)</t>
         </is>
       </c>
       <c r="D5" s="30" t="inlineStr">
@@ -1300,12 +1314,18 @@
       <c r="E5" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="31" t="n"/>
+      <c r="F5" s="31" t="n">
+        <v>0.2</v>
+      </c>
       <c r="G5" s="32">
         <f>IF(OR(E5="",F5=""),"",E5*F5)</f>
         <v/>
       </c>
-      <c r="H5" s="30" t="n"/>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I5" s="33">
         <f>IF(H5="","",INDEX(Liste!$B$2:$B$4,MATCH(H5,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1316,11 +1336,19 @@
       </c>
       <c r="K5" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="L5" s="30" t="inlineStr">
+        <is>
+          <t>D-049</t>
+        </is>
+      </c>
+      <c r="M5" s="30" t="inlineStr">
+        <is>
+          <t>Massa prudente di classe (ZARM MT2-1 0,2 kg; CubeSpace CR0020 2,0 A·m² 54 g). Da confermare con l'unità scelta</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="22">
       <c r="A6" s="28" t="inlineStr">
@@ -2534,7 +2562,7 @@
       </c>
       <c r="C2" s="28" t="inlineStr">
         <is>
-          <t>Ruote di reazione</t>
+          <t>Ruote di reazione (4 in piramide)</t>
         </is>
       </c>
       <c r="D2" s="30" t="inlineStr">
@@ -2542,23 +2570,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E2" s="36" t="n"/>
-      <c r="F2" s="36" t="n"/>
-      <c r="G2" s="36" t="n"/>
-      <c r="H2" s="36" t="n"/>
-      <c r="I2" s="36" t="n"/>
-      <c r="J2" s="30" t="n"/>
+      <c r="E2" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K2" s="33">
         <f>IF(J2="","",INDEX(Liste!$B$2:$B$4,MATCH(J2,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L2" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M2" s="30" t="inlineStr">
+        <is>
+          <t>D-048</t>
+        </is>
+      </c>
+      <c r="N2" s="30" t="inlineStr">
+        <is>
+          <t>4 × BCT RWp100, &lt; 1 W ciascuna a regime. Picco 9 W per ruota in accelerazione (slew, rampe): da considerare nel profilo orbita per orbita (A5.6)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="22">
       <c r="A3" s="28" t="inlineStr">
@@ -2651,7 +2701,7 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>Magnetorquer</t>
+          <t>Magnetorquer (3 barre)</t>
         </is>
       </c>
       <c r="D5" s="30" t="inlineStr">
@@ -2659,23 +2709,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="36" t="n"/>
-      <c r="H5" s="36" t="n"/>
-      <c r="I5" s="36" t="n"/>
-      <c r="J5" s="30" t="n"/>
+      <c r="E5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="K5" s="33">
         <f>IF(J5="","",INDEX(Liste!$B$2:$B$4,MATCH(J5,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L5" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M5" s="30" t="inlineStr">
+        <is>
+          <t>D-049</t>
+        </is>
+      </c>
+      <c r="N5" s="30" t="inlineStr">
+        <is>
+          <t>1 W per barra quando accesa (classe NewSpace NMTR-X, 1 W tipico; ZARM 0,5 W medi). Spente durante le riprese; accese in spinta (scarico) e in safe/detumbling</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="22">
       <c r="A6" s="28" t="inlineStr">

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C3" s="28" t="inlineStr">
         <is>
-          <t>Star tracker</t>
+          <t>Star tracker (2 teste, classe ST-16RT2)</t>
         </is>
       </c>
       <c r="D3" s="30" t="inlineStr">
@@ -1221,13 +1221,21 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="31" t="n"/>
+      <c r="E3" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>0.235</v>
+      </c>
       <c r="G3" s="32">
         <f>IF(OR(E3="",F3=""),"",E3*F3)</f>
         <v/>
       </c>
-      <c r="H3" s="30" t="n"/>
+      <c r="H3" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I3" s="33">
         <f>IF(H3="","",INDEX(Liste!$B$2:$B$4,MATCH(H3,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1238,11 +1246,19 @@
       </c>
       <c r="K3" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L3" s="30" t="inlineStr">
+        <is>
+          <t>D-051</t>
+        </is>
+      </c>
+      <c r="M3" s="30" t="inlineStr">
+        <is>
+          <t>Rocket Lab ST-16RT2 con paraluce grande (158 g senza, 185 g corto, 235 g grande): valore prudente</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="22">
       <c r="A4" s="28" t="inlineStr">
@@ -1257,7 +1273,7 @@
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>Giroscopi / IMU</t>
+          <t>Giroscopio / IMU (classe GY2, inviluppo GY3)</t>
         </is>
       </c>
       <c r="D4" s="30" t="inlineStr">
@@ -1268,12 +1284,18 @@
       <c r="E4" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="31" t="n"/>
+      <c r="F4" s="31" t="n">
+        <v>0.7</v>
+      </c>
       <c r="G4" s="32">
         <f>IF(OR(E4="",F4=""),"",E4*F4)</f>
         <v/>
       </c>
-      <c r="H4" s="30" t="n"/>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I4" s="33">
         <f>IF(H4="","",INDEX(Liste!$B$2:$B$4,MATCH(H4,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1284,11 +1306,19 @@
       </c>
       <c r="K4" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="inlineStr">
+        <is>
+          <t>D-050</t>
+        </is>
+      </c>
+      <c r="M4" s="30" t="inlineStr">
+        <is>
+          <t>Inviluppo KVH 1750 (0,7 kg max). Riferimento di prestazione 3 × CRH03: massa da datasheet completo</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="22">
       <c r="A5" s="28" t="inlineStr">
@@ -1363,7 +1393,7 @@
       </c>
       <c r="C6" s="28" t="inlineStr">
         <is>
-          <t>Magnetometro</t>
+          <t>Magnetometro a 3 assi</t>
         </is>
       </c>
       <c r="D6" s="30" t="inlineStr">
@@ -1374,12 +1404,18 @@
       <c r="E6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="31" t="n"/>
+      <c r="F6" s="31" t="n">
+        <v>0.08500000000000001</v>
+      </c>
       <c r="G6" s="32">
         <f>IF(OR(E6="",F6=""),"",E6*F6)</f>
         <v/>
       </c>
-      <c r="H6" s="30" t="n"/>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I6" s="33">
         <f>IF(H6="","",INDEX(Liste!$B$2:$B$4,MATCH(H6,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1390,11 +1426,19 @@
       </c>
       <c r="K6" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>A5.3 f)</t>
+        </is>
+      </c>
+      <c r="M6" s="30" t="inlineStr">
+        <is>
+          <t>Classe NewSpace NMRM (±60 µT, &lt; 8 nT, 85 g)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="22">
       <c r="A7" s="28" t="inlineStr">
@@ -1409,7 +1453,7 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>Sensori solari</t>
+          <t>Sensori solari grossolani (6 facce)</t>
         </is>
       </c>
       <c r="D7" s="30" t="inlineStr">
@@ -1417,13 +1461,21 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="31" t="n"/>
+      <c r="E7" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>0.035</v>
+      </c>
       <c r="G7" s="32">
         <f>IF(OR(E7="",F7=""),"",E7*F7)</f>
         <v/>
       </c>
-      <c r="H7" s="30" t="n"/>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I7" s="33">
         <f>IF(H7="","",INDEX(Liste!$B$2:$B$4,MATCH(H7,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1434,11 +1486,19 @@
       </c>
       <c r="K7" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L7" s="30" t="n"/>
-      <c r="M7" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>A5.3 f)</t>
+        </is>
+      </c>
+      <c r="M7" s="30" t="inlineStr">
+        <is>
+          <t>Classe NewSpace NCSS-SA05 / NFSS-411: si usa la massa più alta delle due (abbinamento valori-modelli incerto nella fonte)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="22">
       <c r="A8" s="28" t="inlineStr">
@@ -1453,7 +1513,7 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>Ricevitore GNSS + antenna</t>
+          <t>Ricevitore GNSS + antenna (con PPS)</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr">
@@ -1464,12 +1524,18 @@
       <c r="E8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="31" t="n"/>
+      <c r="F8" s="31" t="n">
+        <v>0.075</v>
+      </c>
       <c r="G8" s="32">
         <f>IF(OR(E8="",F8=""),"",E8*F8)</f>
         <v/>
       </c>
-      <c r="H8" s="30" t="n"/>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I8" s="33">
         <f>IF(H8="","",INDEX(Liste!$B$2:$B$4,MATCH(H8,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1480,11 +1546,19 @@
       </c>
       <c r="K8" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L8" s="30" t="n"/>
-      <c r="M8" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>DR-17</t>
+        </is>
+      </c>
+      <c r="M8" s="30" t="inlineStr">
+        <is>
+          <t>Ricevitore classe SkyFox piNAV-NG 24 g (datasheet) + antenna ~50 g (stima). PPS da verificare</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="35.05" customHeight="1" s="22">
       <c r="A9" s="28" t="inlineStr">
@@ -2623,7 +2697,7 @@
       </c>
       <c r="C3" s="28" t="inlineStr">
         <is>
-          <t>Star tracker</t>
+          <t>Star tracker (2 teste)</t>
         </is>
       </c>
       <c r="D3" s="30" t="inlineStr">
@@ -2631,23 +2705,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E3" s="36" t="n"/>
-      <c r="F3" s="36" t="n"/>
-      <c r="G3" s="36" t="n"/>
-      <c r="H3" s="36" t="n"/>
-      <c r="I3" s="36" t="n"/>
-      <c r="J3" s="30" t="n"/>
+      <c r="E3" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K3" s="33">
         <f>IF(J3="","",INDEX(Liste!$B$2:$B$4,MATCH(J3,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L3" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M3" s="30" t="inlineStr">
+        <is>
+          <t>D-051</t>
+        </is>
+      </c>
+      <c r="N3" s="30" t="inlineStr">
+        <is>
+          <t>2 × &lt; 0,5 W medi; picco 1 W ciascuno</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="22">
       <c r="A4" s="28" t="inlineStr">
@@ -2662,7 +2758,7 @@
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>Giroscopi / IMU</t>
+          <t>Giroscopio / IMU</t>
         </is>
       </c>
       <c r="D4" s="30" t="inlineStr">
@@ -2670,23 +2766,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E4" s="36" t="n"/>
-      <c r="F4" s="36" t="n"/>
-      <c r="G4" s="36" t="n"/>
-      <c r="H4" s="36" t="n"/>
-      <c r="I4" s="36" t="n"/>
-      <c r="J4" s="30" t="n"/>
+      <c r="E4" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K4" s="33">
         <f>IF(J4="","",INDEX(Liste!$B$2:$B$4,MATCH(J4,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L4" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M4" s="30" t="inlineStr">
+        <is>
+          <t>D-050</t>
+        </is>
+      </c>
+      <c r="N4" s="30" t="inlineStr">
+        <is>
+          <t>Inviluppo KVH 1750 (5 W tipici, 8 W max)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="22">
       <c r="A5" s="28" t="inlineStr">
@@ -2770,23 +2888,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n"/>
-      <c r="J6" s="30" t="n"/>
+      <c r="E6" s="36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I6" s="36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K6" s="33">
         <f>IF(J6="","",INDEX(Liste!$B$2:$B$4,MATCH(J6,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L6" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M6" s="30" t="inlineStr">
+        <is>
+          <t>A5.3 f)</t>
+        </is>
+      </c>
+      <c r="N6" s="30" t="inlineStr">
+        <is>
+          <t>&lt; 750 mW</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="22">
       <c r="A7" s="28" t="inlineStr">
@@ -2801,7 +2941,7 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>Sensori solari</t>
+          <t>Sensori solari (6)</t>
         </is>
       </c>
       <c r="D7" s="30" t="inlineStr">
@@ -2809,23 +2949,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="36" t="n"/>
-      <c r="I7" s="36" t="n"/>
-      <c r="J7" s="30" t="n"/>
+      <c r="E7" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K7" s="33">
         <f>IF(J7="","",INDEX(Liste!$B$2:$B$4,MATCH(J7,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L7" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M7" s="30" t="n"/>
-      <c r="N7" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M7" s="30" t="inlineStr">
+        <is>
+          <t>A5.3 f)</t>
+        </is>
+      </c>
+      <c r="N7" s="30" t="inlineStr">
+        <is>
+          <t>&lt; 10 mA a 5 V ciascuno</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="22">
       <c r="A8" s="28" t="inlineStr">
@@ -2840,7 +3002,7 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>Ricevitore GNSS + antenna</t>
+          <t>Ricevitore GNSS</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr">
@@ -2848,23 +3010,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="n"/>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="30" t="n"/>
+      <c r="E8" s="36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K8" s="33">
         <f>IF(J8="","",INDEX(Liste!$B$2:$B$4,MATCH(J8,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L8" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M8" s="30" t="n"/>
-      <c r="N8" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M8" s="30" t="inlineStr">
+        <is>
+          <t>DR-17</t>
+        </is>
+      </c>
+      <c r="N8" s="30" t="inlineStr">
+        <is>
+          <t>125 mW tipici (piNAV-NG); antenna passiva/attiva da verificare</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="46.25" customHeight="1" s="22">
       <c r="A9" s="28" t="inlineStr">
@@ -4155,19 +4339,34 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
+      <c r="D4" s="30" t="n">
+        <v>155.7</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>155.7</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <v>155.7</v>
+      </c>
       <c r="G4" s="40">
         <f>IF(OR(D4="",E4="",F4=""),"",D4*E4*F4/1000000)</f>
         <v/>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Calcolo</t>
+        </is>
+      </c>
       <c r="I4" s="30" t="inlineStr">
         <is>
           <t>A5.3</t>
         </is>
       </c>
-      <c r="J4" s="30" t="n"/>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>CUBO EQUIVALENTE (somma dei volumi, 3.77 L), non ingombro reale: il layout si fa in A5.7. Componenti: ruote 4 × 70×70×25; IMU KVH 1750 (ingombro 88,9×88,9×73,7); star tracker 2 × 99×99×120 (paraluce grande); magnetorquer 3 × 13×13×152; magnetometro 99×43×17; GNSS 71×46×11; sensori solari 6 × 34×40×20. Gli star tracker con paraluce grande pesano 2,35 L: con il paraluce corto (62×56×68) scenderebbero a 0,47 L</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="22">
       <c r="A5" s="28" t="inlineStr">

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -569,6 +569,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="22">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -660,6 +661,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="22">
       <c r="A13" s="24" t="inlineStr">
         <is>
@@ -1633,7 +1635,7 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>Radio TT&amp;C (bande da A5.5)</t>
+          <t>Radio TT&amp;C: ricetrasmettitore S (classe XLink-S) + radio VHF/UHF di riserva (classe ISIS)</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr">
@@ -1641,13 +1643,21 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="31" t="n"/>
+      <c r="E10" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>0.275</v>
+      </c>
       <c r="G10" s="32">
         <f>IF(OR(E10="",F10=""),"",E10*F10)</f>
         <v/>
       </c>
-      <c r="H10" s="30" t="n"/>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I10" s="33">
         <f>IF(H10="","",INDEX(Liste!$B$2:$B$4,MATCH(H10,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1658,11 +1668,19 @@
       </c>
       <c r="K10" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>D-082, D-084</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>XLink-S 0,200 kg (&lt; 0,2U) + ISIS VHF/UHF 0,075 kg (90 × 96 × 15 mm). Margine 10%: eredità di volo XLink-S da verificare (R-46). Ripiego R1 (ISIS TXS2 + ricevitore) 0,217 kg</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="22">
       <c r="A11" s="28" t="inlineStr">
@@ -1677,7 +1695,7 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>Antenne TT&amp;C</t>
+          <t>Antenne TT&amp;C: 2 patch S (nadir compatta + zenit) + antenna VHF/UHF dispiegabile</t>
         </is>
       </c>
       <c r="D11" s="30" t="inlineStr">
@@ -1685,13 +1703,21 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="31" t="n"/>
+      <c r="E11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>0.189</v>
+      </c>
       <c r="G11" s="32">
         <f>IF(OR(E11="",F11=""),"",E11*F11)</f>
         <v/>
       </c>
-      <c r="H11" s="30" t="n"/>
+      <c r="H11" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I11" s="33">
         <f>IF(H11="","",INDEX(Liste!$B$2:$B$4,MATCH(H11,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1702,11 +1728,19 @@
       </c>
       <c r="K11" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L11" s="30" t="n"/>
-      <c r="M11" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L11" s="30" t="inlineStr">
+        <is>
+          <t>D-068, D-080, D-082</t>
+        </is>
+      </c>
+      <c r="M11" s="30" t="inlineStr">
+        <is>
+          <t>2 × patch S &lt; 0,050 kg (ISIS; la patch a nadir compatta ≤ 60 mm è TBC, D-080) + ISIS AntS 0,089 kg. Cavi RF nei cablaggi (M-25)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="22">
       <c r="A12" s="28" t="inlineStr">
@@ -2399,6 +2433,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -3116,7 +3151,7 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>Radio TT&amp;C (bande da A5.5)</t>
+          <t>Radio TT&amp;C: ricetrasmettitore S + radio VHF/UHF</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr">
@@ -3124,23 +3159,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
-      <c r="I10" s="36" t="n"/>
-      <c r="J10" s="30" t="n"/>
+      <c r="E10" s="36" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G10" s="36" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H10" s="36" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="I10" s="36" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="K10" s="33">
         <f>IF(J10="","",INDEX(Liste!$B$2:$B$4,MATCH(J10,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L10" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>D-084, D-082</t>
+        </is>
+      </c>
+      <c r="N10" s="30" t="inlineStr">
+        <is>
+          <t>Fuori dai contatti: solo ricevitore VHF sempre acceso (0,48 W). Scarico: XLink-S &lt; 15 W con TX e RX + VHF. Ricevitore S anche ~1,3 h/giorno in sola ricezione attorno ai contatti (&lt; 4 W). Contatti ~71 min/giorno per satellite (in qualunque modo, anche in spinta: D-068). Emergenza UHF in trasmissione 4 W. Energia: TX ~17,7 Wh/giorno + RX S ~5 Wh + VHF ~11,5 Wh ≈ 34 Wh/giorno (profilo in A5.6)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="22">
       <c r="A11" s="28" t="inlineStr">
@@ -3155,7 +3212,7 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>Antenne TT&amp;C</t>
+          <t>Antenne TT&amp;C (passive)</t>
         </is>
       </c>
       <c r="D11" s="30" t="inlineStr">
@@ -3163,23 +3220,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="30" t="n"/>
+      <c r="E11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K11" s="33">
         <f>IF(J11="","",INDEX(Liste!$B$2:$B$4,MATCH(J11,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L11" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M11" s="30" t="inlineStr">
+        <is>
+          <t>D-068, D-080, D-082</t>
+        </is>
+      </c>
+      <c r="N11" s="30" t="inlineStr">
+        <is>
+          <t>Passive. Dispiegamento dell'antenna VHF/UHF una volta sola: 2 W per &lt; 3 s per elemento (ISIS AntS)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="23.85" customHeight="1" s="22">
       <c r="A12" s="28" t="inlineStr">
@@ -3727,6 +3806,7 @@
       <c r="M25" s="30" t="n"/>
       <c r="N25" s="30" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -3835,6 +3915,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>
@@ -3869,7 +3950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="21" min="1" max="1"/>
@@ -4122,15 +4203,19 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="D7" s="39" t="n"/>
-      <c r="E7" s="30" t="n"/>
+      <c r="D7" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" s="40">
         <f>IF(OR(D7="",E7=""),"",D7*E7)</f>
         <v/>
       </c>
       <c r="G7" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Stima</t>
         </is>
       </c>
       <c r="H7" s="30" t="inlineStr">
@@ -4138,15 +4223,20 @@
           <t>A5.5 (Giuliano)</t>
         </is>
       </c>
-      <c r="I7" s="30" t="n"/>
-    </row>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>Telemetria di piattaforma ~5 MB/giorno (stima: ~300 parametri da 2 byte ogni 10 s ≈ 5,2 MB; dati ADCS ad alta frequenza durante le riprese trascurabili). Telemetria del payload ~3 MB/giorno: riga di Giuseppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="22">
       <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Volume giornaliero totale (MB)</t>
         </is>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="41">
         <f>SUM(F2:F7)</f>
         <v/>
       </c>
@@ -4154,8 +4244,11 @@
     <row r="10" ht="23.85" customHeight="1" s="22">
       <c r="B10" s="38" t="inlineStr">
         <is>
-          <t>Capacità di scarico al giorno (MB): da A5.5 (TBD)</t>
-        </is>
+          <t>Capacità di scarico al giorno per satellite (MB): banda S 4,3 Mbit/s, ~71 min/giorno di contatto, 30 s di aggancio per contatto (D-069, A5.5.4)</t>
+        </is>
+      </c>
+      <c r="F10" s="41" t="n">
+        <v>2030</v>
       </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="22">
@@ -4163,6 +4256,17 @@
         <is>
           <t>Memoria di bordo: margine RAM ≥ 50%, processore ≤ 50% (D-035)</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Uso della capacità (volume / capacità)</t>
+        </is>
+      </c>
+      <c r="F12" s="41">
+        <f>IF(F9="","",F9/F10)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4352,7 +4456,7 @@
         <f>IF(OR(D4="",E4="",F4=""),"",D4*E4*F4/1000000)</f>
         <v/>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>Calcolo</t>
         </is>
@@ -4384,19 +4488,34 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
+      <c r="D5" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>80</v>
+      </c>
       <c r="G5" s="40">
         <f>IF(OR(D5="",E5="",F5=""),"",D5*E5*F5/1000000)</f>
         <v/>
       </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>Calcolo</t>
+        </is>
+      </c>
       <c r="I5" s="30" t="inlineStr">
         <is>
-          <t>A5.5</t>
-        </is>
-      </c>
-      <c r="J5" s="30" t="n"/>
+          <t>A5.5, D-084</t>
+        </is>
+      </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>CUBO EQUIVALENTE (somma dei volumi), non ingombro reale: XLink-S ~0,2 L (&lt; 0,2U); ISIS VHF/UHF 90 × 96 × 15; AntS 98 × 98 × 7 (su una faccia esterna); 2 patch S ~80 × 80 × 9 (la nadir compatta ≤ 60 × 60, D-080). Posizioni in A5.7</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="22">
       <c r="A6" s="28" t="inlineStr">
@@ -4480,6 +4599,7 @@
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="30" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -569,7 +569,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="22">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -661,7 +660,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="22">
       <c r="A13" s="24" t="inlineStr">
         <is>
@@ -2433,7 +2431,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -3551,7 +3548,7 @@
       </c>
       <c r="D19" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E19" s="36" t="n"/>
@@ -3569,7 +3566,11 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="M19" s="30" t="n"/>
+      <c r="M19" s="30" t="inlineStr">
+        <is>
+          <t>D-087</t>
+        </is>
+      </c>
       <c r="N19" s="30" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="22">
@@ -3590,7 +3591,7 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E20" s="36" t="n"/>
@@ -3608,7 +3609,11 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="M20" s="30" t="n"/>
+      <c r="M20" s="30" t="inlineStr">
+        <is>
+          <t>D-087</t>
+        </is>
+      </c>
       <c r="N20" s="30" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="22">
@@ -3629,7 +3634,7 @@
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E21" s="36" t="n"/>
@@ -3647,7 +3652,11 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="M21" s="30" t="n"/>
+      <c r="M21" s="30" t="inlineStr">
+        <is>
+          <t>D-087</t>
+        </is>
+      </c>
       <c r="N21" s="30" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="22">
@@ -3806,7 +3815,6 @@
       <c r="M25" s="30" t="n"/>
       <c r="N25" s="30" t="n"/>
     </row>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -3915,7 +3923,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>
@@ -4229,7 +4236,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="22">
       <c r="B9" s="34" t="inlineStr">
         <is>
@@ -4599,7 +4605,6 @@
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="30" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -3278,23 +3278,45 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="30" t="n"/>
+      <c r="E12" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="K12" s="33">
         <f>IF(J12="","",INDEX(Liste!$B$2:$B$4,MATCH(J12,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L12" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M12" s="30" t="n"/>
-      <c r="N12" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M12" s="30" t="inlineStr">
+        <is>
+          <t>D-088 (Proposta), D-090</t>
+        </is>
+      </c>
+      <c r="N12" s="30" t="inlineStr">
+        <is>
+          <t>Nessun consumo proprio: i riscaldatori del telescopio stanno in P-23. Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="22">
       <c r="A13" s="28" t="inlineStr">
@@ -3317,23 +3339,45 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
-      <c r="I13" s="36" t="n"/>
-      <c r="J13" s="30" t="n"/>
+      <c r="E13" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="K13" s="33">
         <f>IF(J13="","",INDEX(Liste!$B$2:$B$4,MATCH(J13,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L13" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M13" s="30" t="n"/>
-      <c r="N13" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M13" s="30" t="inlineStr">
+        <is>
+          <t>D-024, D-032</t>
+        </is>
+      </c>
+      <c r="N13" s="30" t="inlineStr">
+        <is>
+          <t>Classe Sony IMX342: camera commerciale con lo stesso sensore 5,3 W tipici a 25 fps 12 bit (Imperx CXP-C6440). Acceso ~8 min per passaggio con riprese, spento fuori. Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="22">
       <c r="A14" s="28" t="inlineStr">
@@ -3356,23 +3400,45 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
-      <c r="I14" s="36" t="n"/>
-      <c r="J14" s="30" t="n"/>
+      <c r="E14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="K14" s="33">
         <f>IF(J14="","",INDEX(Liste!$B$2:$B$4,MATCH(J14,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L14" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M14" s="30" t="n"/>
-      <c r="N14" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M14" s="30" t="inlineStr">
+        <is>
+          <t>D-026, D-089</t>
+        </is>
+      </c>
+      <c r="N14" s="30" t="inlineStr">
+        <is>
+          <t>Classe Gpixel GSENSE400BSI: sensore &lt; 0,6 W + elettronica di lettura. Acceso ~8 min per passaggio notturno. Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="22">
       <c r="A15" s="28" t="inlineStr">
@@ -3395,23 +3461,45 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="36" t="n"/>
-      <c r="I15" s="36" t="n"/>
-      <c r="J15" s="30" t="n"/>
+      <c r="E15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="K15" s="33">
         <f>IF(J15="","",INDEX(Liste!$B$2:$B$4,MATCH(J15,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L15" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M15" s="30" t="n"/>
-      <c r="N15" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M15" s="30" t="inlineStr">
+        <is>
+          <t>D-079</t>
+        </is>
+      </c>
+      <c r="N15" s="30" t="inlineStr">
+        <is>
+          <t>Motorino passo-passo ~2 W per ~10 s a movimento, nessun consumo da fermo; ~4 movimenti/giorno = ~0,02 Wh (trascurabile, picco da considerare nel profilo). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="22">
       <c r="A16" s="28" t="inlineStr">
@@ -3434,23 +3522,45 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
-      <c r="J16" s="30" t="n"/>
+      <c r="E16" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="K16" s="33">
         <f>IF(J16="","",INDEX(Liste!$B$2:$B$4,MATCH(J16,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L16" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M16" s="30" t="n"/>
-      <c r="N16" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M16" s="30" t="inlineStr">
+        <is>
+          <t>D-081, D-085, D-086</t>
+        </is>
+      </c>
+      <c r="N16" s="30" t="inlineStr">
+        <is>
+          <t>FPGA + memoria ~6 W mentre somma (~10 min per passaggio), ~2 W in attesa; chip AI ~2 W mentre elabora (~1–2 min per passaggio), ~0,2 W in attesa. Ripresa = FPGA + AI accesi (picco payload 13 W di giorno con P-12, 10 W di notte). Scarico = scheda in attesa perché la coda sta nella sua memoria (D-086). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="22">
       <c r="A17" s="28" t="inlineStr">
@@ -3473,23 +3583,45 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="30" t="n"/>
+      <c r="E17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="K17" s="33">
         <f>IF(J17="","",INDEX(Liste!$B$2:$B$4,MATCH(J17,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L17" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M17" s="30" t="n"/>
-      <c r="N17" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M17" s="30" t="inlineStr">
+        <is>
+          <t>D-086</t>
+        </is>
+      </c>
+      <c r="N17" s="30" t="inlineStr">
+        <is>
+          <t>Inclusa in P-15 (FPGA + memoria). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="22">
       <c r="A18" s="28" t="inlineStr">
@@ -3758,23 +3890,45 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="30" t="n"/>
+      <c r="E24" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="K24" s="33">
         <f>IF(J24="","",INDEX(Liste!$B$2:$B$4,MATCH(J24,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L24" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M24" s="30" t="n"/>
-      <c r="N24" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M24" s="30" t="inlineStr">
+        <is>
+          <t>DR-03</t>
+        </is>
+      </c>
+      <c r="N24" s="30" t="inlineStr">
+        <is>
+          <t>~4 W di picco su telescopio e sensori per il fuoco entro ±37 µm, contati sempre accesi (~96 Wh/giorno) finché A5.P7 non dà il ciclo: valore prudente, voce più grande e più incerta del payload. In safe ~2 W (sopravvivenza): nella colonna Riposo/safe resta 4 W, caso prudente. Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="22">
       <c r="A25" s="28" t="inlineStr">

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>Telescopio TMA (specchi + struttura ottica)</t>
+          <t>Telescopio RC + 3 lenti, vetro + carbonio (D-088, D-090), con piastra del piano focale</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
@@ -1764,12 +1764,18 @@
       <c r="E12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="31" t="n"/>
+      <c r="F12" s="31" t="n">
+        <v>1.595</v>
+      </c>
       <c r="G12" s="32">
         <f>IF(OR(E12="",F12=""),"",E12*F12)</f>
         <v/>
       </c>
-      <c r="H12" s="30" t="n"/>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="I12" s="33">
         <f>IF(H12="","",INDEX(Liste!$B$2:$B$4,MATCH(H12,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1780,7 +1786,7 @@
       </c>
       <c r="K12" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="L12" s="30" t="n"/>
@@ -1810,12 +1816,18 @@
       <c r="E13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="31" t="n"/>
+      <c r="F13" s="31" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G13" s="32">
         <f>IF(OR(E13="",F13=""),"",E13*F13)</f>
         <v/>
       </c>
-      <c r="H13" s="30" t="n"/>
+      <c r="H13" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="I13" s="33">
         <f>IF(H13="","",INDEX(Liste!$B$2:$B$4,MATCH(H13,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1826,7 +1838,7 @@
       </c>
       <c r="K13" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="L13" s="30" t="n"/>
@@ -1856,12 +1868,18 @@
       <c r="E14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="31" t="n"/>
+      <c r="F14" s="31" t="n">
+        <v>0.22</v>
+      </c>
       <c r="G14" s="32">
         <f>IF(OR(E14="",F14=""),"",E14*F14)</f>
         <v/>
       </c>
-      <c r="H14" s="30" t="n"/>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="I14" s="33">
         <f>IF(H14="","",INDEX(Liste!$B$2:$B$4,MATCH(H14,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1872,7 +1890,7 @@
       </c>
       <c r="K14" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="L14" s="30" t="n"/>
@@ -1891,7 +1909,7 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>Deflettori / coperchio apertura</t>
+          <t>Paraluce esterno 10 cm + coperchio motorizzato (D-079)</t>
         </is>
       </c>
       <c r="D15" s="30" t="inlineStr">
@@ -1899,13 +1917,21 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="31" t="n"/>
+      <c r="E15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <v>0.3</v>
+      </c>
       <c r="G15" s="32">
         <f>IF(OR(E15="",F15=""),"",E15*F15)</f>
         <v/>
       </c>
-      <c r="H15" s="30" t="n"/>
+      <c r="H15" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="I15" s="33">
         <f>IF(H15="","",INDEX(Liste!$B$2:$B$4,MATCH(H15,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1916,7 +1942,7 @@
       </c>
       <c r="K15" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="L15" s="30" t="n"/>
@@ -1935,7 +1961,7 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>Scheda AI / elaborazione payload</t>
+          <t>Scheda payload: FPGA + chip AI + scatola (D-085)</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
@@ -1946,12 +1972,18 @@
       <c r="E16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="31" t="n"/>
+      <c r="F16" s="31" t="n">
+        <v>0.45</v>
+      </c>
       <c r="G16" s="32">
         <f>IF(OR(E16="",F16=""),"",E16*F16)</f>
         <v/>
       </c>
-      <c r="H16" s="30" t="n"/>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I16" s="33">
         <f>IF(H16="","",INDEX(Liste!$B$2:$B$4,MATCH(H16,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -1962,7 +1994,7 @@
       </c>
       <c r="K16" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="L16" s="30" t="n"/>
@@ -1981,7 +2013,7 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>Memoria di massa</t>
+          <t>Memoria di massa 32 GB (sulla scheda FPGA, D-086)</t>
         </is>
       </c>
       <c r="D17" s="30" t="inlineStr">
@@ -1989,13 +2021,21 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="31" t="n"/>
+      <c r="E17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>0.02</v>
+      </c>
       <c r="G17" s="32">
         <f>IF(OR(E17="",F17=""),"",E17*F17)</f>
         <v/>
       </c>
-      <c r="H17" s="30" t="n"/>
+      <c r="H17" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I17" s="33">
         <f>IF(H17="","",INDEX(Liste!$B$2:$B$4,MATCH(H17,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2006,7 +2046,7 @@
       </c>
       <c r="K17" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="L17" s="30" t="n"/>
@@ -2303,13 +2343,21 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="31" t="n"/>
+      <c r="E24" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>0.18</v>
+      </c>
       <c r="G24" s="32">
         <f>IF(OR(E24="",F24=""),"",E24*F24)</f>
         <v/>
       </c>
-      <c r="H24" s="30" t="n"/>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="I24" s="33">
         <f>IF(H24="","",INDEX(Liste!$B$2:$B$4,MATCH(H24,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2320,7 +2368,7 @@
       </c>
       <c r="K24" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="L24" s="30" t="n"/>
@@ -2431,6 +2479,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -4565,7 +4614,7 @@
       </c>
       <c r="B3" s="28" t="inlineStr">
         <is>
-          <t>Telescopio TMA</t>
+          <t>Telescopio RC con paraluce e coperchio (D-088)</t>
         </is>
       </c>
       <c r="C3" s="30" t="inlineStr">
@@ -4573,19 +4622,34 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
+      <c r="D3" s="30" t="n">
+        <v>140</v>
+      </c>
+      <c r="E3" s="30" t="n">
+        <v>140</v>
+      </c>
+      <c r="F3" s="30" t="n">
+        <v>410</v>
+      </c>
       <c r="G3" s="40">
         <f>IF(OR(D3="",E3="",F3=""),"",D3*E3*F3/1000000)</f>
         <v/>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Calcolo</t>
+        </is>
+      </c>
       <c r="I3" s="30" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="J3" s="30" t="n"/>
+          <t>D-088, D-078</t>
+        </is>
+      </c>
+      <c r="J3" s="30" t="inlineStr">
+        <is>
+          <t>Colonna contro un lato della faccia a nadir (asse a Y −43 mm); Z da 0 (coperchio) a ~410 mm (sensori). a5_calcoli/p4_massa_baricentro.py</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="22">
       <c r="A4" s="28" t="inlineStr">
@@ -4693,19 +4757,34 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
+      <c r="D6" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>60</v>
+      </c>
       <c r="G6" s="40">
         <f>IF(OR(D6="",E6="",F6=""),"",D6*E6*F6/1000000)</f>
         <v/>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Stima</t>
+        </is>
+      </c>
       <c r="I6" s="30" t="inlineStr">
         <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="J6" s="30" t="n"/>
+          <t>D-085, D-086</t>
+        </is>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>Scatola della scheda FPGA + chip AI, TBC alla scelta della scheda; posizione proposta vicino ai sensori (cavi corti a 7,5 Gbit/s)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="22">
       <c r="A7" s="28" t="inlineStr">
@@ -4759,6 +4838,7 @@
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="30" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2479,7 +2479,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -3319,7 +3318,7 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>Telescopio TMA (specchi + struttura ottica)</t>
+          <t>Telescopio RC (specchi, lenti, struttura ottica)</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
@@ -3602,12 +3601,12 @@
       </c>
       <c r="M16" s="30" t="inlineStr">
         <is>
-          <t>D-081, D-085, D-086</t>
+          <t>D-081, D-085, D-086, D-092</t>
         </is>
       </c>
       <c r="N16" s="30" t="inlineStr">
         <is>
-          <t>FPGA + memoria ~6 W mentre somma (~10 min per passaggio), ~2 W in attesa; chip AI ~2 W mentre elabora (~1–2 min per passaggio), ~0,2 W in attesa. Ripresa = FPGA + AI accesi (picco payload 13 W di giorno con P-12, 10 W di notte). Scarico = scheda in attesa perché la coda sta nella sua memoria (D-086). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+          <t>FPGA + memoria ~6 W mentre somma (~10 min per passaggio), ~2 W in attesa; chip AI ~2 W mentre elabora (~1–2 min per passaggio), ~0,2 W in attesa. Ripresa = FPGA + AI accesi (picco payload 13 W di giorno con P-12, 10 W di notte). Scarico = scheda in attesa perché la coda sta nella sua memoria (D-086). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py) | D-092 (Q1): in attesa solo durante i contatti (~71 min/giorno, ~2,5 Wh/giorno), spenta nel resto del riposo</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4634,7 @@
         <f>IF(OR(D3="",E3="",F3=""),"",D3*E3*F3/1000000)</f>
         <v/>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>Calcolo</t>
         </is>
@@ -4770,7 +4769,7 @@
         <f>IF(OR(D6="",E6="",F6=""),"",D6*E6*F6/1000000)</f>
         <v/>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>Stima</t>
         </is>
@@ -4838,7 +4837,6 @@
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="30" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -3413,17 +3413,17 @@
       </c>
       <c r="L13" s="30" t="inlineStr">
         <is>
-          <t>Stima</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="M13" s="30" t="inlineStr">
         <is>
-          <t>D-024, D-032</t>
+          <t>D-093, D-097</t>
         </is>
       </c>
       <c r="N13" s="30" t="inlineStr">
         <is>
-          <t>Classe Sony IMX342: camera commerciale con lo stesso sensore 5,3 W tipici a 25 fps 12 bit (Imperx CXP-C6440). Acceso ~8 min per passaggio con riprese, spento fuori. Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+          <t>Classe Sony IMX342: camera Imperx CXP-C6440 con lo stesso sensore 5,3 W tipici a 25 fps 12 bit; con il rallentamento (D-096) bastano ~10 immagini/s, 5 W tenuto prudente. Acceso ~8 min per passaggio diurno con riprese. a5_calcoli/p6_potenza.py</t>
         </is>
       </c>
     </row>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="L14" s="30" t="inlineStr">
         <is>
-          <t>Stima</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="M14" s="30" t="inlineStr">
         <is>
-          <t>D-026, D-089</t>
+          <t>D-094, D-097</t>
         </is>
       </c>
       <c r="N14" s="30" t="inlineStr">
         <is>
-          <t>Classe Gpixel GSENSE400BSI: sensore &lt; 0,6 W + elettronica di lettura. Acceso ~8 min per passaggio notturno. Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+          <t>Classe Gpixel GSENSE400BSI: sensore &lt; 0,6 W (scheda prodotto) + elettronica di lettura ~1,4 W (stima). Acceso ~8 min per passaggio notturno</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="M15" s="30" t="inlineStr">
         <is>
-          <t>D-079</t>
+          <t>D-079, D-097</t>
         </is>
       </c>
       <c r="N15" s="30" t="inlineStr">
         <is>
-          <t>Motorino passo-passo ~2 W per ~10 s a movimento, nessun consumo da fermo; ~4 movimenti/giorno = ~0,02 Wh (trascurabile, picco da considerare nel profilo). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+          <t>Motorino ~2 W per ~10 s a movimento (~4 movimenti/giorno, ~0,02 Wh/giorno): trascurabile nei modi</t>
         </is>
       </c>
     </row>
@@ -3571,23 +3571,23 @@
         </is>
       </c>
       <c r="E16" s="36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="I16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="30" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Catalogo modificato</t>
         </is>
       </c>
       <c r="K16" s="33">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="L16" s="30" t="inlineStr">
         <is>
-          <t>Stima</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="M16" s="30" t="inlineStr">
         <is>
-          <t>D-081, D-085, D-086, D-092</t>
+          <t>D-085, D-092, D-097</t>
         </is>
       </c>
       <c r="N16" s="30" t="inlineStr">
         <is>
-          <t>FPGA + memoria ~6 W mentre somma (~10 min per passaggio), ~2 W in attesa; chip AI ~2 W mentre elabora (~1–2 min per passaggio), ~0,2 W in attesa. Ripresa = FPGA + AI accesi (picco payload 13 W di giorno con P-12, 10 W di notte). Scarico = scheda in attesa perché la coda sta nella sua memoria (D-086). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py) | D-092 (Q1): in attesa solo durante i contatti (~71 min/giorno, ~2,5 Wh/giorno), spenta nel resto del riposo</t>
+          <t>Scheda FPGA classe Xiphos Q8 (Zynq UltraScale+ ZU7EG, 5 W tipici, 3,5–25 W, in volo dal 2020) + chip AI classe Ubotica CogniSAT-XE1 (Myriad 2, 2 W tipici, 5 W max, TRL 9). Ripresa: FPGA 5 + AI 2 W (FPGA ~10 min, AI ~2 min per passaggio). Scarico: solo FPGA al minimo della classe 3,5 W (AI spento), ~71 min/giorno (D-092) = ~4,1 Wh/giorno</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="J17" s="30" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Catalogo</t>
         </is>
       </c>
       <c r="K17" s="33">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="L17" s="30" t="inlineStr">
         <is>
-          <t>Stima</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="M17" s="30" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="N17" s="30" t="inlineStr">
         <is>
-          <t>Inclusa in P-15 (FPGA + memoria). Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+          <t>Inclusa in P-15 (memoria sulla scheda FPGA)</t>
         </is>
       </c>
     </row>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -3357,7 +3357,7 @@
       </c>
       <c r="M12" s="30" t="inlineStr">
         <is>
-          <t>D-088 (Proposta), D-090</t>
+          <t>D-088, D-090</t>
         </is>
       </c>
       <c r="N12" s="30" t="inlineStr">

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>Telescopio RC + 3 lenti, vetro + carbonio (D-088, D-090), con piastra del piano focale</t>
+          <t>Telescopio RC + 3 lenti, specchi Zerodur, aste Invar + guscio in carbonio (D-088, D-090, D-098), con piastra del piano focale</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
@@ -3945,13 +3945,13 @@
         <v>4</v>
       </c>
       <c r="G24" s="36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24" s="36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" s="36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" s="30" t="inlineStr">
         <is>
@@ -3969,12 +3969,12 @@
       </c>
       <c r="M24" s="30" t="inlineStr">
         <is>
-          <t>DR-03</t>
+          <t>D-100, D-095, DR-57</t>
         </is>
       </c>
       <c r="N24" s="30" t="inlineStr">
         <is>
-          <t>~4 W di picco su telescopio e sensori per il fuoco entro ±37 µm, contati sempre accesi (~96 Wh/giorno) finché A5.P7 non dà il ciclo: valore prudente, voce più grande e più incerta del payload. In safe ~2 W (sopravvivenza): nella colonna Riposo/safe resta 4 W, caso prudente. Valori di Giuseppe del 30/10/2026, provvisori TBC fino ad A5.P6/A5.P7 (a5_calcoli/p6_potenza_provvisoria.py)</t>
+          <t>Riscaldatori del telescopio regolato entro ±11 K (D-098, DR-57): ~4 W di picco a coperchio aperto (riprese), ~2 W medi con coperchio chiuso, ~1 W in safe (solo sopravvivenza). Stima a5_calcoli/p7_termico.py, TBC fino al modello termico di Fase B (dipende dalla temperatura interna della piattaforma)</t>
         </is>
       </c>
     </row>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -3945,13 +3945,13 @@
         <v>4</v>
       </c>
       <c r="G24" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="36" t="n">
         <v>2</v>
-      </c>
-      <c r="H24" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="36" t="n">
-        <v>1</v>
       </c>
       <c r="J24" s="30" t="inlineStr">
         <is>
@@ -4017,6 +4017,7 @@
       <c r="M25" s="30" t="n"/>
       <c r="N25" s="30" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -4125,6 +4126,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuseppe</t>
         </is>
       </c>
       <c r="E25" s="30" t="n"/>
@@ -2479,6 +2479,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -3996,7 +3997,7 @@
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuseppe</t>
         </is>
       </c>
       <c r="E25" s="36" t="n"/>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2479,7 +2479,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -3180,7 +3179,7 @@
       </c>
       <c r="N9" s="30" t="inlineStr">
         <is>
-          <t>Spinta 50 W nominali (30–60 W). Inviluppo di picco 75 W (BIT-3, D-034). Riscaldamento e mantenimento in temperatura dello iodio: TBD. ESA: per l'elettronica EP il margine voce va solo sulla potenza dissipata</t>
+          <t>Spinta 50 W nominali (30–60 W). Inviluppo di picco 75 W (BIT-3, D-034). Riscaldamento e mantenimento in temperatura dello iodio: TBD. ESA: per l'elettronica EP il margine voce va solo sulla potenza dissipata | D-104: 50 W d'ingresso considerati comprensivi del riscaldamento dello iodio (non dato a parte nel datasheet), TBC con T4i; compatibilità con bus 12–16,8 V da verificare (D-109). D-112: acceso solo con SoC ≥ 90%</t>
         </is>
       </c>
     </row>
@@ -3693,23 +3692,45 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="30" t="n"/>
+      <c r="E18" s="36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G18" s="36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J18" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K18" s="33">
         <f>IF(J18="","",INDEX(Liste!$B$2:$B$4,MATCH(J18,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L18" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M18" s="30" t="n"/>
-      <c r="N18" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="M18" s="30" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+      <c r="N18" s="30" t="inlineStr">
+        <is>
+          <t>Classe ISIS iOBC, 400 mW medi (TBC finché non si sceglie l'OBC, D-038)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="22">
       <c r="A19" s="28" t="inlineStr">
@@ -3732,27 +3753,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="30" t="n"/>
+      <c r="E19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="K19" s="33">
         <f>IF(J19="","",INDEX(Liste!$B$2:$B$4,MATCH(J19,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L19" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="M19" s="30" t="inlineStr">
         <is>
-          <t>D-087</t>
-        </is>
-      </c>
-      <c r="N19" s="30" t="n"/>
+          <t>D-106, D-108</t>
+        </is>
+      </c>
+      <c r="N19" s="30" t="inlineStr">
+        <is>
+          <t>Sorgente, non carico (0 W). 6 ali 226 × 454 mm, 9 celle Azur 3G30-Advanced ciascuna: 130 W a Sole perpendicolare a fine vita, 74,5 W medi in luce (k 0,575, D-106)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="22">
       <c r="A20" s="28" t="inlineStr">
@@ -3775,27 +3814,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="30" t="n"/>
+      <c r="E20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K20" s="33">
         <f>IF(J20="","",INDEX(Liste!$B$2:$B$4,MATCH(J20,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L20" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="M20" s="30" t="inlineStr">
         <is>
-          <t>D-087</t>
-        </is>
-      </c>
-      <c r="N20" s="30" t="n"/>
+          <t>D-109, D-111</t>
+        </is>
+      </c>
+      <c r="N20" s="30" t="inlineStr">
+        <is>
+          <t>Accumulo, non carico (0 W). Li-ion 4S3P, 12 celle 18650 2,6 Ah, 112 Wh, bus 12–16,8 V; scarica ≤ 25% a fine vita (≤ 35% con una stringa guasta), simulazione 20,4% / 30,7%</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="22">
       <c r="A21" s="28" t="inlineStr">
@@ -3818,27 +3875,45 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="30" t="n"/>
+      <c r="E21" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F21" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J21" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="K21" s="33">
         <f>IF(J21="","",INDEX(Liste!$B$2:$B$4,MATCH(J21,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L21" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="M21" s="30" t="inlineStr">
         <is>
-          <t>D-087</t>
-        </is>
-      </c>
-      <c r="N21" s="30" t="n"/>
+          <t>D-087, D-104</t>
+        </is>
+      </c>
+      <c r="N21" s="30" t="inlineStr">
+        <is>
+          <t>Consumo a vuoto classe GomSpace NanoPower P60 (ACU-200 + PDU-200), 600 mW (TBC). Rendimento di conversione (~90% MPPT) a parte, nel dimensionamento dei pannelli</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="22">
       <c r="A22" s="28" t="inlineStr">
@@ -4016,9 +4091,12 @@
         </is>
       </c>
       <c r="M25" s="30" t="n"/>
-      <c r="N25" s="30" t="n"/>
-    </row>
-    <row r="26"/>
+      <c r="N25" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Riscaldatori della batteria TBD (D-104, D-109): dal modello termico di Giuseppe (D-110), temperatura interna ~15–20 °C (DR-64)</t>
+        </is>
+      </c>
+    </row>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -4127,7 +4205,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -167,7 +167,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -295,6 +295,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +700,7 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Consumi per modo operativo; media sull'orbita in A5.6.</t>
+          <t>Consumi per modo operativo; media sull'orbita e profilo da A5.6 (sotto i totali).</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="21" min="1" max="1"/>
@@ -4208,7 +4209,126 @@
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>Media sull'orbita e profilo eclisse/luce: da A5.6 (TBD)</t>
+          <t>Media sull'orbita e profilo eclisse/luce (A5.6, PULSE_EPS/A5.6; valori di calcolo, non formule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>Orbita: luce minima / eclisse massima (D-102)</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>54,5 / 36,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>Giorno di routine, Sole medio, con margini (A5.6.3)</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>Wh/giorno</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>809 (media 33,7 W)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>Giorno di emergenza 2+2, con margini</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>Wh/giorno</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>Giorno con Sole alto (7,8 h di spinta), con margini</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>Wh/giorno</t>
+        </is>
+      </c>
+      <c r="E36" s="43" t="inlineStr">
+        <is>
+          <t>1050 (non coperto: R-56, regola D-112)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>Pannelli 6 ali, medi in luce a fine vita (D-106, D-108)</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E37" s="43" t="inlineStr">
+        <is>
+          <t>74,5 (130 a Sole perpendicolare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>Batteria 4S3P: stato di carica minimo routine / con una stringa guasta (A5.6.7)</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="inlineStr">
+        <is>
+          <t>79,6 / 69,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>Avanzo di energia, routine (A5.6.7)</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>Wh/giorno</t>
+        </is>
+      </c>
+      <c r="E39" s="43" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
     </row>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2117,7 +2117,7 @@
       </c>
       <c r="D19" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E19" s="30" t="n"/>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E20" s="30" t="n"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E21" s="30" t="n">
@@ -2480,6 +2480,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -5024,7 +5025,7 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="D8" s="30" t="n"/>
@@ -5037,6 +5038,7 @@
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="30" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2480,7 +2480,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -4077,28 +4076,47 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="36" t="n"/>
-      <c r="H25" s="36" t="n"/>
-      <c r="I25" s="36" t="n"/>
-      <c r="J25" s="30" t="n"/>
+      <c r="E25" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F25" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G25" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H25" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I25" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="J25" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="K25" s="33">
         <f>IF(J25="","",INDEX(Liste!$B$2:$B$4,MATCH(J25,Liste!$A$2:$A$4,0)))</f>
         <v/>
       </c>
       <c r="L25" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M25" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="M25" s="30" t="inlineStr">
+        <is>
+          <t>D-116, DR-68</t>
+        </is>
+      </c>
       <c r="N25" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Riscaldatori della batteria TBD (D-104, D-109): dal modello termico di Giuseppe (D-110), temperatura interna ~15–20 °C (DR-64)</t>
-        </is>
-      </c>
-    </row>
+          <t>Allocazione (D-116 approvata 31/10/2026): riprese, spinta e scarico 2,8 W nominali = tetto di DR-68 (≤ 4 W medi al bus con margine voce 20% e di sistema 20%), giorno peggiore di routine; riposo/safe 9 W (stima di primo ordine di Giuseppe, A5.8.2: con margini SoC minimo in safe ~75%, ok). Giorno senza spinta ~11 W: chiude perché il motore è spento. Valori da sostituire con il modello a nodi (A5.8.3) | Riscaldatori della batteria compresi (D-104, D-109); interno 15–25 °C (DR-64)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -4207,6 +4225,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>
@@ -4789,20 +4808,25 @@
         <v>95</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G2" s="40">
         <f>IF(OR(D2="",E2="",F2=""),"",D2*E2*F2/1000000)</f>
         <v/>
       </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>Stima</t>
+        </is>
+      </c>
       <c r="I2" s="30" t="inlineStr">
         <is>
-          <t>D-034</t>
+          <t>D-034, D-117</t>
         </is>
       </c>
       <c r="J2" s="30" t="inlineStr">
         <is>
-          <t>Valore prudente (l'altra tabella T4I dà 200 mm). DA VERIFICARE IN A5.7: con l'orientamento L1 (D-043) la spinta è lungo X, dove l'involucro è 226,3 mm: con 250 mm l'unità non entra se l'ugello è in testata; controllare disegno T4I</t>
+          <t>Due blocchi (D-117): motore + elettronica con ugello su −X e serbatoio separato, 2,2U in tutto (EarthNext Tab. 3). Z = somma delle profondità dei due blocchi a pari sezione (2,2 L / (93,8 × 95 mm)); ripartizione TBC (ICD T4i). Fetta disponibile su −X con D-118: ~86 mm (~126 mm con la sporgenza)</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5062,6 @@
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="30" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2077,12 +2077,18 @@
       <c r="E18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="31" t="n"/>
+      <c r="F18" s="31" t="n">
+        <v>0.1</v>
+      </c>
       <c r="G18" s="32">
         <f>IF(OR(E18="",F18=""),"",E18*F18)</f>
         <v/>
       </c>
-      <c r="H18" s="30" t="n"/>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I18" s="33">
         <f>IF(H18="","",INDEX(Liste!$B$2:$B$4,MATCH(H18,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2093,11 +2099,19 @@
       </c>
       <c r="K18" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L18" s="30" t="n"/>
-      <c r="M18" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L18" s="30" t="inlineStr">
+        <is>
+          <t>D-104, D-121</t>
+        </is>
+      </c>
+      <c r="M18" s="30" t="inlineStr">
+        <is>
+          <t>Classe ISIS iOBC: 76 g scheda, 100 g con scheda figlia; 96 × 90 × 12,4 mm; −25/+65 °C. Responsabile secondo D-113 (Proposta)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="22">
       <c r="A19" s="28" t="inlineStr">
@@ -2120,13 +2134,21 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="31" t="n"/>
+      <c r="E19" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>0.55</v>
+      </c>
       <c r="G19" s="32">
         <f>IF(OR(E19="",F19=""),"",E19*F19)</f>
         <v/>
       </c>
-      <c r="H19" s="30" t="n"/>
+      <c r="H19" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I19" s="33">
         <f>IF(H19="","",INDEX(Liste!$B$2:$B$4,MATCH(H19,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2137,11 +2159,19 @@
       </c>
       <c r="K19" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L19" s="30" t="n"/>
-      <c r="M19" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="L19" s="30" t="inlineStr">
+        <is>
+          <t>D-106, D-108, D-119</t>
+        </is>
+      </c>
+      <c r="M19" s="30" t="inlineStr">
+        <is>
+          <t>6 ali 226 × 454 mm (S1, substrato FR4/alluminio): 5,0–5,5 kg/m² con celle a catalogo (AAC Photon 3U 135 g, ISIS 3U 150 g) × 0,103 m²; celle 118 g per ala (D-108). Con 8 ali (R-56) +1,1 kg</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="22">
       <c r="A20" s="28" t="inlineStr">
@@ -2164,13 +2194,21 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="31" t="n"/>
+      <c r="E20" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>0.75</v>
+      </c>
       <c r="G20" s="32">
         <f>IF(OR(E20="",F20=""),"",E20*F20)</f>
         <v/>
       </c>
-      <c r="H20" s="30" t="n"/>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I20" s="33">
         <f>IF(H20="","",INDEX(Liste!$B$2:$B$4,MATCH(H20,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2181,11 +2219,19 @@
       </c>
       <c r="K20" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L20" s="30" t="n"/>
-      <c r="M20" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="L20" s="30" t="inlineStr">
+        <is>
+          <t>D-109, D-121</t>
+        </is>
+      </c>
+      <c r="M20" s="30" t="inlineStr">
+        <is>
+          <t>4S3P, 12 celle 18650 2,6 Ah: 62,5 g per cella scalati da GomSpace BPX (500 g per 8 celle, con elettronica e riscaldatori da 6 W)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="22">
       <c r="A21" s="28" t="inlineStr">
@@ -2211,12 +2257,18 @@
       <c r="E21" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="31" t="n"/>
+      <c r="F21" s="31" t="n">
+        <v>0.282</v>
+      </c>
       <c r="G21" s="32">
         <f>IF(OR(E21="",F21=""),"",E21*F21)</f>
         <v/>
       </c>
-      <c r="H21" s="30" t="n"/>
+      <c r="H21" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo</t>
+        </is>
+      </c>
       <c r="I21" s="33">
         <f>IF(H21="","",INDEX(Liste!$B$2:$B$4,MATCH(H21,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2227,11 +2279,19 @@
       </c>
       <c r="K21" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L21" s="30" t="n"/>
-      <c r="M21" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L21" s="30" t="inlineStr">
+        <is>
+          <t>D-104, D-121</t>
+        </is>
+      </c>
+      <c r="M21" s="30" t="inlineStr">
+        <is>
+          <t>Classe GomSpace P60: base &lt; 80 g + 2 ACU × 54 g + 2 PDU × 47 g (2 ACU per avere ingressi anche per 8 ali); 92 × 88,9 × 28,9 mm; −35/+85 °C</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="22">
       <c r="A22" s="28" t="inlineStr">
@@ -2257,12 +2317,18 @@
       <c r="E22" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="31" t="n"/>
+      <c r="F22" s="31" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G22" s="32">
         <f>IF(OR(E22="",F22=""),"",E22*F22)</f>
         <v/>
       </c>
-      <c r="H22" s="30" t="n"/>
+      <c r="H22" s="30" t="inlineStr">
+        <is>
+          <t>Catalogo modificato</t>
+        </is>
+      </c>
       <c r="I22" s="33">
         <f>IF(H22="","",INDEX(Liste!$B$2:$B$4,MATCH(H22,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2273,11 +2339,19 @@
       </c>
       <c r="K22" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L22" s="30" t="n"/>
-      <c r="M22" s="30" t="n"/>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="L22" s="30" t="inlineStr">
+        <is>
+          <t>D-036, D-120</t>
+        </is>
+      </c>
+      <c r="M22" s="30" t="inlineStr">
+        <is>
+          <t>Classe EnduroSat 16U (Al 6082, 226,3 × 226,3 × 454 mm, viti e 6 anelli compresi). Catalogo modificato: attacchi per ali, motore e radiatore. Responsabile secondo D-113 (Proposta)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="22">
       <c r="A23" s="28" t="inlineStr">
@@ -2300,13 +2374,21 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="31" t="n"/>
+      <c r="E23" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="31" t="n">
+        <v>0.06</v>
+      </c>
       <c r="G23" s="32">
         <f>IF(OR(E23="",F23=""),"",E23*F23)</f>
         <v/>
       </c>
-      <c r="H23" s="30" t="n"/>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="I23" s="33">
         <f>IF(H23="","",INDEX(Liste!$B$2:$B$4,MATCH(H23,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2317,11 +2399,19 @@
       </c>
       <c r="K23" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L23" s="30" t="n"/>
-      <c r="M23" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="L23" s="30" t="inlineStr">
+        <is>
+          <t>D-106, D-121</t>
+        </is>
+      </c>
+      <c r="M23" s="30" t="inlineStr">
+        <is>
+          <t>2 cerniere a molla + 1 sgancio (classe filo che brucia o vite termica) per ala, ~60 g per ala: stima di primo ordine, nessuna fonte con massa (TBC). Responsabile secondo D-113 (Proposta)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="22">
       <c r="A24" s="28" t="inlineStr">
@@ -4116,7 +4206,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -4225,7 +4314,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>
@@ -5026,15 +5114,34 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="30" t="n"/>
+      <c r="D7" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>12.4</v>
+      </c>
       <c r="G7" s="40">
         <f>IF(OR(D7="",E7="",F7=""),"",D7*E7*F7/1000000)</f>
         <v/>
       </c>
-      <c r="I7" s="30" t="n"/>
-      <c r="J7" s="30" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>D-104, D-121</t>
+        </is>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>Classe ISIS iOBC (formato PC104)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="22">
       <c r="A8" s="28" t="inlineStr">
@@ -5052,15 +5159,34 @@
           <t>Giuliano</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="30" t="n"/>
-      <c r="F8" s="30" t="n"/>
+      <c r="D8" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>89</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>90.90000000000001</v>
+      </c>
       <c r="G8" s="40">
         <f>IF(OR(D8="",E8="",F8=""),"",D8*E8*F8/1000000)</f>
         <v/>
       </c>
-      <c r="I8" s="30" t="n"/>
-      <c r="J8" s="30" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>D-104, D-109, D-121</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>Pila PC104: PCDU P60 92 × 88,9 × 28,9 mm + batteria 4S3P ~93 × 86 × 62 mm (stima scalata da GomSpace BPX 93 × 86 × 41 per 8 celle). Altezza = somma</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2486,13 +2486,21 @@
           <t>Giuseppe</t>
         </is>
       </c>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="31" t="n"/>
+      <c r="E25" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="31" t="n">
+        <v>0.45</v>
+      </c>
       <c r="G25" s="32">
         <f>IF(OR(E25="",F25=""),"",E25*F25)</f>
         <v/>
       </c>
-      <c r="H25" s="30" t="n"/>
+      <c r="H25" s="30" t="inlineStr">
+        <is>
+          <t>Nuovo</t>
+        </is>
+      </c>
       <c r="I25" s="33">
         <f>IF(H25="","",INDEX(Liste!$B$2:$B$4,MATCH(H25,Liste!$A$2:$A$4,0)))</f>
         <v/>
@@ -2503,11 +2511,19 @@
       </c>
       <c r="K25" s="30" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L25" s="30" t="n"/>
-      <c r="M25" s="30" t="n"/>
+          <t>Stima</t>
+        </is>
+      </c>
+      <c r="L25" s="30" t="inlineStr">
+        <is>
+          <t>D-116, D-122</t>
+        </is>
+      </c>
+      <c r="M25" s="30" t="inlineStr">
+        <is>
+          <t>MLI sul corpo ~0,26 m² × ~0,35 kg/m² ≈ 0,09 kg; radiatore Al 1 mm 600 cm² + vernice ≈ 0,17 kg; collegamenti termici e rinforzi ≈ 0,15 kg; riscaldatori, termostati e sensori ≈ 0,04 kg. Stima di primo ordine (A5.8.4), TBC</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.85" customHeight="1" s="22">
       <c r="A26" s="28" t="inlineStr">
@@ -4167,19 +4183,19 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="F25" s="36" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="G25" s="36" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="H25" s="36" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="I25" s="36" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
@@ -4192,17 +4208,17 @@
       </c>
       <c r="L25" s="30" t="inlineStr">
         <is>
-          <t>Stima</t>
+          <t>Calcolo</t>
         </is>
       </c>
       <c r="M25" s="30" t="inlineStr">
         <is>
-          <t>D-116, DR-68</t>
+          <t>D-116, D-122, DR-68</t>
         </is>
       </c>
       <c r="N25" s="30" t="inlineStr">
         <is>
-          <t>Allocazione (D-116 approvata 31/10/2026): riprese, spinta e scarico 2,8 W nominali = tetto di DR-68 (≤ 4 W medi al bus con margine voce 20% e di sistema 20%), giorno peggiore di routine; riposo/safe 9 W (stima di primo ordine di Giuseppe, A5.8.2: con margini SoC minimo in safe ~75%, ok). Giorno senza spinta ~11 W: chiude perché il motore è spento. Valori da sostituire con il modello a nodi (A5.8.3) | Riscaldatori della batteria compresi (D-104, D-109); interno 15–25 °C (DR-64)</t>
+          <t>Modello a nodi A5.8.3 (a5_8_3_modello_nodi.py, radiatore 600 cm²): riprese, spinta e scarico 0,7 W = media del giorno peggiore di routine (fine maggio-giugno, 17 Wh/giorno; DR-68 ≤ 2,8 W); riposo/safe 5,7 W = giorno senza spinta, caso più freddo (137 Wh/giorno, picco 15 W); safe vero e proprio ~0,4 W. Riscaldatori della batteria compresi (D-104). Sostituisce l'allocazione 2,8/9 W di Giuliano (31/10/2026)</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5143,7 @@
         <f>IF(OR(D7="",E7="",F7=""),"",D7*E7*F7/1000000)</f>
         <v/>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>Datasheet</t>
         </is>
@@ -5172,7 +5188,7 @@
         <f>IF(OR(D8="",E8="",F8=""),"",D8*E8*F8/1000000)</f>
         <v/>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>Stima</t>
         </is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D18" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E18" s="30" t="n">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="M18" s="30" t="inlineStr">
         <is>
-          <t>Classe ISIS iOBC: 76 g scheda, 100 g con scheda figlia; 96 × 90 × 12,4 mm; −25/+65 °C. Responsabile secondo D-113 (Proposta)</t>
+          <t>Classe ISIS iOBC: 76 g scheda, 100 g con scheda figlia; 96 × 90 × 12,4 mm; −25/+65 °C</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E22" s="30" t="n">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="M22" s="30" t="inlineStr">
         <is>
-          <t>Classe EnduroSat 16U (Al 6082, 226,3 × 226,3 × 454 mm, viti e 6 anelli compresi). Catalogo modificato: attacchi per ali, motore e radiatore. Responsabile secondo D-113 (Proposta)</t>
+          <t>Classe EnduroSat 16U (Al 6082, 226,3 × 226,3 × 454 mm, viti e 6 anelli compresi). Catalogo modificato: attacchi per ali, motore e radiatore</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E23" s="30" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="M23" s="30" t="inlineStr">
         <is>
-          <t>2 cerniere a molla + 1 sgancio (classe filo che brucia o vite termica) per ala, ~60 g per ala: stima di primo ordine, nessuna fonte con massa (TBC). Responsabile secondo D-113 (Proposta)</t>
+          <t>2 cerniere a molla + 1 sgancio (classe filo che brucia o vite termica) per ala, ~60 g per ala: stima di primo ordine, nessuna fonte con massa (TBC)</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D26" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E26" s="28" t="n">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D18" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E18" s="36" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E22" s="36" t="n"/>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="E23" s="36" t="n"/>
@@ -4218,10 +4218,11 @@
       </c>
       <c r="N25" s="30" t="inlineStr">
         <is>
-          <t>Modello a nodi A5.8.3 (a5_8_3_modello_nodi.py, radiatore 600 cm²): riprese, spinta e scarico 0,7 W = media del giorno peggiore di routine (fine maggio-giugno, 17 Wh/giorno; DR-68 ≤ 2,8 W); riposo/safe 5,7 W = giorno senza spinta, caso più freddo (137 Wh/giorno, picco 15 W); safe vero e proprio ~0,4 W. Riscaldatori della batteria compresi (D-104). Sostituisce l'allocazione 2,8/9 W di Giuliano (31/10/2026)</t>
-        </is>
-      </c>
-    </row>
+          <t>Modello a nodi A5.8.3 (a5_8_3_modello_nodi.py, radiatore 600 cm²): riprese, spinta e scarico 0,7 W = media del giorno peggiore di routine (fine maggio-giugno, 17 Wh/giorno; DR-68 ≤ 2,8 W); riposo/safe 5,7 W = giorno senza spinta, caso più freddo (137 Wh/giorno, picco 15 W); safe vero e proprio ~0,4 W. Riscaldatori della batteria compresi (D-104). Sostituisce l'allocazione 2,8/9 W di Giuliano (31/10/2026) | 31/10/2026: D-122 approvata da Giuliano (0,7 W nei modi operativi, 5,7 W in riposo = giorno senza spinta, 0,4 W in safe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -4330,6 +4331,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>
@@ -5127,7 +5129,7 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="D7" s="30" t="n">

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -1226,7 +1226,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="31" t="n">
-        <v>0.235</v>
+        <v>0.185</v>
       </c>
       <c r="G3" s="32">
         <f>IF(OR(E3="",F3=""),"",E3*F3)</f>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="L3" s="30" t="inlineStr">
         <is>
-          <t>D-051</t>
+          <t>D-051, D-123</t>
         </is>
       </c>
       <c r="M3" s="30" t="inlineStr">
         <is>
-          <t>Rocket Lab ST-16RT2 con paraluce grande (158 g senza, 185 g corto, 235 g grande): valore prudente</t>
+          <t>Rocket Lab ST-16RT2 con paraluce corto (D-123): 185 g per testa, 62 × 56 × 68 mm (158 g senza, 235 g con il grande)</t>
         </is>
       </c>
     </row>
@@ -2586,6 +2586,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -4222,7 +4223,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="C27" s="34" t="inlineStr">
         <is>
@@ -4331,7 +4331,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="23.85" customHeight="1" s="22">
       <c r="C32" s="38" t="inlineStr">
         <is>
@@ -4998,13 +4997,13 @@
         </is>
       </c>
       <c r="D4" s="30" t="n">
-        <v>155.7</v>
+        <v>123.6</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>155.7</v>
+        <v>123.6</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>155.7</v>
+        <v>123.6</v>
       </c>
       <c r="G4" s="40">
         <f>IF(OR(D4="",E4="",F4=""),"",D4*E4*F4/1000000)</f>
@@ -5022,7 +5021,7 @@
       </c>
       <c r="J4" s="30" t="inlineStr">
         <is>
-          <t>CUBO EQUIVALENTE (somma dei volumi, 3.77 L), non ingombro reale: il layout si fa in A5.7. Componenti: ruote 4 × 70×70×25; IMU KVH 1750 (ingombro 88,9×88,9×73,7); star tracker 2 × 99×99×120 (paraluce grande); magnetorquer 3 × 13×13×152; magnetometro 99×43×17; GNSS 71×46×11; sensori solari 6 × 34×40×20. Gli star tracker con paraluce grande pesano 2,35 L: con il paraluce corto (62×56×68) scenderebbero a 0,47 L</t>
+          <t>CUBO EQUIVALENTE (somma dei volumi, 3.77 L), non ingombro reale: il layout si fa in A5.7. Componenti: ruote 4 × 70×70×25; IMU KVH 1750 (ingombro 88,9×88,9×73,7); star tracker 2 × 99×99×120 (paraluce grande); magnetorquer 3 × 13×13×152; magnetometro 99×43×17; GNSS 71×46×11; sensori solari 6 × 34×40×20. Gli star tracker con paraluce grande pesano 2,35 L: con il paraluce corto (62×56×68) scenderebbero a 0,47 L | 31/10/2026 (D-123): star tracker con paraluce corto (0,47 L invece di 2,35 L): cubo equivalente 1,89 L (lato 123,6 mm)</t>
         </is>
       </c>
     </row>
@@ -5206,6 +5205,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>

--- a/PULSE_Budget_FaseA.xlsx
+++ b/PULSE_Budget_FaseA.xlsx
@@ -2586,7 +2586,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="22">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -4184,19 +4183,19 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="F25" s="36" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="G25" s="36" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H25" s="36" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="I25" s="36" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
@@ -4214,12 +4213,12 @@
       </c>
       <c r="M25" s="30" t="inlineStr">
         <is>
-          <t>D-116, D-122, DR-68</t>
+          <t>D-116, D-122, D-128, DR-68</t>
         </is>
       </c>
       <c r="N25" s="30" t="inlineStr">
         <is>
-          <t>Modello a nodi A5.8.3 (a5_8_3_modello_nodi.py, radiatore 600 cm²): riprese, spinta e scarico 0,7 W = media del giorno peggiore di routine (fine maggio-giugno, 17 Wh/giorno; DR-68 ≤ 2,8 W); riposo/safe 5,7 W = giorno senza spinta, caso più freddo (137 Wh/giorno, picco 15 W); safe vero e proprio ~0,4 W. Riscaldatori della batteria compresi (D-104). Sostituisce l'allocazione 2,8/9 W di Giuliano (31/10/2026) | 31/10/2026: D-122 approvata da Giuliano (0,7 W nei modi operativi, 5,7 W in riposo = giorno senza spinta, 0,4 W in safe)</t>
+          <t>Modello a nodi A5.8.3 (a5_8_3_modello_nodi.py, radiatore 600 cm²): riprese, spinta e scarico 0,7 W = media del giorno peggiore di routine (fine maggio-giugno, 17 Wh/giorno; DR-68 ≤ 2,8 W); riposo/safe 5,7 W = giorno senza spinta, caso più freddo (137 Wh/giorno, picco 15 W); safe vero e proprio ~0,4 W. Riscaldatori della batteria compresi (D-104). Sostituisce l'allocazione 2,8/9 W di Giuliano (31/10/2026) | 31/10/2026: D-122 approvata da Giuliano (0,7 W nei modi operativi, 5,7 W in riposo = giorno senza spinta, 0,4 W in safe) | 31/10/2026 (A5.8.7, D-128, Proposta): con il layout L1b e le ali W1 (interno a due nodi) 1,1 W nei modi operativi (26 Wh/giorno) e 5,9 W in riposo (giorno senza spinta, 144 Wh/giorno); inviluppo delle sensibilità 2,0/7,0 W</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5204,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="B10" s="34" t="inlineStr">
         <is>
